--- a/artfynd/A 42391-2021 artfynd.xlsx
+++ b/artfynd/A 42391-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42391-2021 artfynd.xlsx
+++ b/artfynd/A 42391-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2057,6 +2057,113 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129702614</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56916</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nydala, Nydala, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>763388</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7089669</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Carl Wiking</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Carl Wiking</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42391-2021 artfynd.xlsx
+++ b/artfynd/A 42391-2021 artfynd.xlsx
@@ -2062,7 +2062,7 @@
         <v>129702614</v>
       </c>
       <c r="B14" t="n">
-        <v>56916</v>
+        <v>56917</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 42391-2021 artfynd.xlsx
+++ b/artfynd/A 42391-2021 artfynd.xlsx
@@ -2062,7 +2062,7 @@
         <v>129702614</v>
       </c>
       <c r="B14" t="n">
-        <v>56917</v>
+        <v>56918</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 42391-2021 artfynd.xlsx
+++ b/artfynd/A 42391-2021 artfynd.xlsx
@@ -2062,7 +2062,7 @@
         <v>129702614</v>
       </c>
       <c r="B14" t="n">
-        <v>56918</v>
+        <v>56921</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 42391-2021 artfynd.xlsx
+++ b/artfynd/A 42391-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2164,6 +2164,118 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130855767</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nydala, Nydala, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>763684</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7089644</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Carl Wiking</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Carl Wiking</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42391-2021 artfynd.xlsx
+++ b/artfynd/A 42391-2021 artfynd.xlsx
@@ -2281,7 +2281,7 @@
         <v>132316472</v>
       </c>
       <c r="B16" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>132316434</v>
       </c>
       <c r="B17" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 42391-2021 artfynd.xlsx
+++ b/artfynd/A 42391-2021 artfynd.xlsx
@@ -2281,7 +2281,7 @@
         <v>132316472</v>
       </c>
       <c r="B16" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>132316434</v>
       </c>
       <c r="B17" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 42391-2021 artfynd.xlsx
+++ b/artfynd/A 42391-2021 artfynd.xlsx
@@ -2281,7 +2281,7 @@
         <v>132316472</v>
       </c>
       <c r="B16" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>132316434</v>
       </c>
       <c r="B17" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 42391-2021 artfynd.xlsx
+++ b/artfynd/A 42391-2021 artfynd.xlsx
@@ -2281,7 +2281,7 @@
         <v>132316472</v>
       </c>
       <c r="B16" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>132316434</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 42391-2021 artfynd.xlsx
+++ b/artfynd/A 42391-2021 artfynd.xlsx
@@ -2281,7 +2281,7 @@
         <v>132316472</v>
       </c>
       <c r="B16" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>132316434</v>
       </c>
       <c r="B17" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 42391-2021 artfynd.xlsx
+++ b/artfynd/A 42391-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>107585</v>
       </c>
       <c r="B2" t="n">
-        <v>77540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>763740.5835561909</v>
+        <v>763741</v>
       </c>
       <c r="R2" t="n">
-        <v>7089423.540202457</v>
+        <v>7089424</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2009-07-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-07-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,12 +780,7 @@
         <v>107586</v>
       </c>
       <c r="B3" t="n">
-        <v>77540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>763750.5563670036</v>
+        <v>763751</v>
       </c>
       <c r="R3" t="n">
-        <v>7089447.436480211</v>
+        <v>7089447</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,9 @@
           <t>2009-07-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2009-07-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88404619</v>
+        <v>88404606</v>
       </c>
       <c r="B4" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>763325.2798994188</v>
+        <v>763335</v>
       </c>
       <c r="R4" t="n">
-        <v>7089652.804871393</v>
+        <v>7089617</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -982,19 +947,9 @@
           <t>2020-10-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-10-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,12 +979,7 @@
         <v>88404607</v>
       </c>
       <c r="B5" t="n">
-        <v>89732</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1061,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>763335.7041550854</v>
+        <v>763336</v>
       </c>
       <c r="R5" t="n">
-        <v>7089613.338177419</v>
+        <v>7089613</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1094,19 +1044,9 @@
           <t>2020-10-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-10-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,37 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88404606</v>
+        <v>88404619</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>763334.9299059515</v>
+        <v>763325</v>
       </c>
       <c r="R6" t="n">
-        <v>7089617.263105069</v>
+        <v>7089653</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1206,19 +1141,9 @@
           <t>2020-10-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-10-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,15 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104504578</v>
+        <v>112344188</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,47 +1181,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Umeå, Vb</t>
+          <t>Umeå, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>763588.5503104471</v>
+        <v>763543</v>
       </c>
       <c r="R7" t="n">
-        <v>7089668.322424635</v>
+        <v>7089426</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,22 +1236,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-11-06</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-11-06</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,15 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104823469</v>
+        <v>112292298</v>
       </c>
       <c r="B8" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,47 +1289,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>5448</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Umeå, Vb</t>
+          <t>Umeå, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>763537.5129827429</v>
+        <v>763579</v>
       </c>
       <c r="R8" t="n">
-        <v>7089446.778403656</v>
+        <v>7089647</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,22 +1344,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-11-26</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-11-26</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,15 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112292298</v>
+        <v>112344251</v>
       </c>
       <c r="B9" t="n">
-        <v>90898</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,26 +1406,26 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Umeå (Umeå), Vb</t>
+          <t>Umeå, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>763579</v>
+        <v>763530</v>
       </c>
       <c r="R9" t="n">
-        <v>7089646</v>
+        <v>7089425</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,22 +1452,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1602,15 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112344251</v>
+        <v>112344211</v>
       </c>
       <c r="B10" t="n">
-        <v>90898</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,35 +1505,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Umeå (Umeå), Vb</t>
+          <t>Umeå, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>763530</v>
+        <v>763527</v>
       </c>
       <c r="R10" t="n">
-        <v>7089425</v>
+        <v>7089456</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1565,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,7 +1575,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,51 +1602,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112344211</v>
+        <v>132316434</v>
       </c>
       <c r="B11" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Umeå (Umeå), Vb</t>
+          <t>Garnlav vid försöksplatsen, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>763527</v>
+        <v>763637</v>
       </c>
       <c r="R11" t="n">
-        <v>7089456</v>
+        <v>7089620</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,22 +1667,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,63 +1697,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>André Larencranz</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>André Larencranz</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112344188</v>
+        <v>132316472</v>
       </c>
       <c r="B12" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Umeå (Umeå), Vb</t>
+          <t>Garnlav vid försöksplatsen 2, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>763543</v>
+        <v>763582</v>
       </c>
       <c r="R12" t="n">
-        <v>7089426</v>
+        <v>7089616</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,22 +1774,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,44 +1804,39 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>André Larencranz</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>André Larencranz</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112780331</v>
+        <v>130855767</v>
       </c>
       <c r="B13" t="n">
-        <v>57342</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102125</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1975,25 +1845,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Umeå (Umeå), Vb</t>
+          <t>Nydala, Nydala, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>763408</v>
+        <v>763684</v>
       </c>
       <c r="R13" t="n">
-        <v>7089666</v>
+        <v>7089644</v>
       </c>
       <c r="S13" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2017,22 +1881,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,39 +1916,39 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>André Larencranz</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>André Larencranz</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129702614</v>
+        <v>112780331</v>
       </c>
       <c r="B14" t="n">
-        <v>56921</v>
+        <v>58592</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>102125</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2088,19 +1957,25 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nydala, Nydala, Vb</t>
+          <t>Umeå, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>763388</v>
+        <v>763408</v>
       </c>
       <c r="R14" t="n">
-        <v>7089669</v>
+        <v>7089666</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2124,22 +1999,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,39 +2029,39 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Carl Wiking</t>
+          <t>André Larencranz</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Carl Wiking</t>
+          <t>André Larencranz</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130855767</v>
+        <v>129702614</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2201,13 +2076,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>763684</v>
+        <v>763388</v>
       </c>
       <c r="R15" t="n">
-        <v>7089644</v>
+        <v>7089669</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2231,27 +2106,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2278,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132316472</v>
+        <v>104823469</v>
       </c>
       <c r="B16" t="n">
-        <v>79332</v>
+        <v>58114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,37 +2159,47 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Garnlav vid försöksplatsen 2, Vb</t>
+          <t>Umeå, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>763582</v>
+        <v>763538</v>
       </c>
       <c r="R16" t="n">
-        <v>7089616</v>
+        <v>7089447</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2343,22 +2223,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2022-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2022-11-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2373,60 +2253,72 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>André Larencranz</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>André Larencranz</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132316434</v>
+        <v>111119766</v>
       </c>
       <c r="B17" t="n">
-        <v>79332</v>
+        <v>99038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Garnlav vid försöksplatsen, Vb</t>
+          <t>Nydalaskogen, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>763637</v>
+        <v>763296</v>
       </c>
       <c r="R17" t="n">
-        <v>7089620</v>
+        <v>7089642</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2450,22 +2342,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2474,18 +2366,24 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Tallsumpskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Helena Lindblom</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Helena Lindblom</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 42391-2021 artfynd.xlsx
+++ b/artfynd/A 42391-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107585</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107586</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88404606</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88404607</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88404619</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1275,6 +1305,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112344188</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,6 +1418,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112292298</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1491,6 +1531,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112344251</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1599,6 +1644,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112344211</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1706,6 +1756,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132316434</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1813,6 +1868,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132316472</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1925,6 +1985,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130855767</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2038,6 +2103,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112780331</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2145,6 +2215,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129702614</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2262,6 +2337,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104823469</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2387,8 +2467,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111119766</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>